--- a/Config/Datas/EntityDatas/EntityData.xlsx
+++ b/Config/Datas/EntityDatas/EntityData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\EntityDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB8BFD6-31BA-4873-BC19-ED424DF04F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D597688-989B-49E3-BD3C-8AA59D0EAFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,6 +136,22 @@
   </si>
   <si>
     <t>实体描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石壁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一堵石壁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没啥效果，就是比较坚硬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stein</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -206,17 +222,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -227,11 +234,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,9 +530,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -535,34 +551,34 @@
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="5" t="s">
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -581,34 +597,34 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="4" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -628,14 +644,14 @@
         <v>13</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="2"/>
@@ -646,7 +662,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -658,39 +674,39 @@
       <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
       <c r="Q4" t="s">
         <v>19</v>
       </c>
       <c r="R4" t="s">
         <v>23</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="4" t="s">
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -700,36 +716,36 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="8" t="s">
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="S5" s="9" t="s">
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="S5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="T5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8" t="s">
+      <c r="U5" s="12"/>
+      <c r="V5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -739,390 +755,400 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="8" t="s">
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="10" t="s">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
       <c r="R8" s="2"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
       <c r="V8" s="2"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="9"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="9"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="9"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="9"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
       <c r="N18" s="3"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="15">
